--- a/data/raw/inventory/Week 27/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1096,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>52</v>
       </c>
       <c r="K12" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
         <v>244</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K18" t="n">
         <v>256</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F65" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G65" t="n">
         <v>32</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K65" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L65" t="n">
         <v>7</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F67" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>6</v>
       </c>
       <c r="K67" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -4999,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K74" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L74" t="n">
         <v>23</v>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F105" t="n">
         <v>44</v>
@@ -6921,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>24</v>
       </c>
       <c r="F147" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K147" t="n">
         <v>24</v>
@@ -9761,7 +9761,7 @@
         <v>106</v>
       </c>
       <c r="F151" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -9773,7 +9773,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K151" t="n">
         <v>106</v>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F167" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>62</v>
       </c>
       <c r="K167" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -11187,7 +11187,7 @@
         <v>139</v>
       </c>
       <c r="F174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11199,7 +11199,7 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K174" t="n">
         <v>142</v>
@@ -12055,7 +12055,7 @@
         <v>40</v>
       </c>
       <c r="F188" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K188" t="n">
         <v>40</v>
@@ -12179,7 +12179,7 @@
         <v>9</v>
       </c>
       <c r="F190" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -12191,7 +12191,7 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K190" t="n">
         <v>9</v>

--- a/data/raw/inventory/Week 27/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
         <v>40</v>
@@ -1096,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K12" t="n">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F18" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         <v>55</v>
       </c>
       <c r="K18" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F20" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20" t="n">
         <v>3</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>148</v>
       </c>
       <c r="F25" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G25" t="n">
         <v>10</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>149</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
         <v>14</v>
@@ -2194,25 +2194,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F29" t="n">
+        <v>183</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>184</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>186</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>43</v>
       </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>43</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F35" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G35" t="n">
         <v>20</v>
@@ -2584,7 +2584,7 @@
         <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F36" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F37" t="n">
         <v>30</v>
@@ -2705,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F39" t="n">
         <v>59</v>
@@ -2829,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F40" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G40" t="n">
         <v>5</v>
@@ -2894,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F41" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G41" t="n">
         <v>40</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K41" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F44" t="n">
         <v>75</v>
@@ -3139,13 +3139,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L44" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M44" t="n">
         <v>3</v>
@@ -3375,7 +3375,7 @@
         <v>32</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
         <v>33</v>
@@ -4116,7 +4116,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -4131,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F62" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -4255,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F65" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="G65" t="n">
         <v>32</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K65" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L65" t="n">
         <v>7</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F67" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -5002,10 +5002,10 @@
         <v>140</v>
       </c>
       <c r="K74" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="L74" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F76" t="n">
         <v>31</v>
@@ -5123,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F80" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L80" t="n">
         <v>9</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F82" t="n">
         <v>223</v>
@@ -5495,13 +5495,13 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
         <v>232</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
         <v>1</v>
@@ -6366,10 +6366,10 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="F101" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G101" t="n">
         <v>40</v>
@@ -6676,7 +6676,7 @@
         <v>2</v>
       </c>
       <c r="K101" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -6723,7 +6723,7 @@
         <v>276</v>
       </c>
       <c r="F102" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G102" t="n">
         <v>8</v>
@@ -6735,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102" t="n">
         <v>279</v>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F104" t="n">
         <v>28</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F105" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F108" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G108" t="n">
         <v>94</v>
@@ -7107,13 +7107,13 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K108" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F109" t="n">
         <v>47</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K109" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F111" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K111" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F112" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K112" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>39</v>
       </c>
       <c r="F113" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7417,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
         <v>39</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -8270,10 +8270,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F127" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8285,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L127" t="n">
         <v>4</v>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F129" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -8409,10 +8409,10 @@
         <v>9</v>
       </c>
       <c r="J129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K129" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
@@ -8769,7 +8769,7 @@
         <v>20</v>
       </c>
       <c r="F135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -8781,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
         <v>20</v>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F139" t="n">
         <v>20</v>
@@ -9029,10 +9029,10 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F142" t="n">
         <v>54</v>
@@ -9215,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9386,11 +9386,11 @@
         </is>
       </c>
       <c r="E145" t="n">
+        <v>23</v>
+      </c>
+      <c r="F145" t="n">
         <v>21</v>
       </c>
-      <c r="F145" t="n">
-        <v>20</v>
-      </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
@@ -9401,10 +9401,10 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F151" t="n">
         <v>103</v>
@@ -9773,10 +9773,10 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K151" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -9947,7 +9947,7 @@
         <v>55</v>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
         <v>48</v>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K154" t="n">
         <v>55</v>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F167" t="n">
         <v>22</v>
@@ -10765,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K167" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -11013,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L171" t="n">
         <v>1</v>
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11199,13 +11199,13 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K174" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="L174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F175" t="n">
         <v>39</v>
@@ -11261,10 +11261,10 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K175" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
         <v>23</v>
       </c>
       <c r="F177" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11385,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K177" t="n">
         <v>24</v>
@@ -11928,7 +11928,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F186" t="n">
         <v>45</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K186" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L186" t="n">
         <v>1</v>
@@ -12055,7 +12055,7 @@
         <v>40</v>
       </c>
       <c r="F188" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K188" t="n">
         <v>40</v>
